--- a/submissions/02-title-exam-cedarbrook-lot12/inputs/tax_and_lien_search_hlt262214.xlsx
+++ b/submissions/02-title-exam-cedarbrook-lot12/inputs/tax_and_lien_search_hlt262214.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C19E89-F681-A047-A9FF-7975BAA6215C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDD28C1-D24E-1F40-A06E-A12973D11A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tax Duplicate" sheetId="1" r:id="rId1"/>
     <sheet name="Judgment Liens" sheetId="2" r:id="rId2"/>
-    <sheet name="Names" sheetId="3" r:id="rId3"/>
+    <sheet name="Docket Entries" sheetId="3" r:id="rId3"/>
+    <sheet name="Names" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="154">
   <si>
     <t>Licking County Treasurer - tax duplicate inquiry, parcel 048-112-00.000</t>
   </si>
   <si>
-    <t>418 Cedarbrook Drive, Newark. Owner of record: OKAFOR TAMSIN. Legal: LOT 12 &amp; N 1/2 LOT 13 CEDARBROOK SUB. Inquiry printed 10/02/2026.</t>
+    <t>418 Cedarbrook Drive, Newark. Owner of record: BELLO TAMSIN N. Legal: LOT 12 &amp; N 42.25 FT LOT 13 CEDARBROOK SUB. Inquiry printed 10/02/2026.</t>
   </si>
   <si>
     <t>TAX YEAR</t>
@@ -52,18 +53,30 @@
     <t>First half</t>
   </si>
   <si>
+    <t>02/15/2023</t>
+  </si>
+  <si>
+    <t>02/09/2023</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Second half</t>
+  </si>
+  <si>
+    <t>07/19/2023</t>
+  </si>
+  <si>
+    <t>07/12/2023</t>
+  </si>
+  <si>
     <t>02/20/2024</t>
   </si>
   <si>
     <t>02/14/2024</t>
   </si>
   <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>Second half</t>
-  </si>
-  <si>
     <t>07/19/2024</t>
   </si>
   <si>
@@ -85,10 +98,13 @@
     <t>02/18/2026</t>
   </si>
   <si>
+    <t>02/24/2026</t>
+  </si>
+  <si>
     <t>07/20/2026</t>
   </si>
   <si>
-    <t>Delinquent</t>
+    <t>Unpaid</t>
   </si>
   <si>
     <t>Special assessment: Cedarbrook sanitary sewer improvement, 20 annual installments of 625.00 certified to the duplicate in 2015, collected half with each installment.</t>
@@ -100,10 +116,10 @@
     <t>Tax year 2026 values and rates are not yet certified; the 2026 duplicate will be payable in 2027.</t>
   </si>
   <si>
-    <t>Licking County Clerk of Courts - judgment lien search, names searched as listed on the Names tab</t>
-  </si>
-  <si>
-    <t>Search run 10/02/2026 against the judgment lien docket, 10-year look-back. Interest accrues at the rate stated in the judgment entry.</t>
+    <t>Licking County Clerk of Courts - judgment lien docket, names searched as listed on the Names tab</t>
+  </si>
+  <si>
+    <t>Docket run 10/02/2026 for certificates filed on or after 01/01/2006. Later filings under each certificate are on the Docket Entries tab.</t>
   </si>
   <si>
     <t>JL NUMBER</t>
@@ -112,6 +128,9 @@
     <t>FILED</t>
   </si>
   <si>
+    <t>JUDGMENT DATE</t>
+  </si>
+  <si>
     <t>JUDGMENT CREDITOR</t>
   </si>
   <si>
@@ -130,25 +149,181 @@
     <t>RATE</t>
   </si>
   <si>
+    <t>10JL00227</t>
+  </si>
+  <si>
+    <t>03/12/2010</t>
+  </si>
+  <si>
+    <t>02/23/2010</t>
+  </si>
+  <si>
+    <t>Licking Memorial Health Systems</t>
+  </si>
+  <si>
+    <t>Pruitt Daniel R</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 09CVF03388, Licking Memorial Health Systems v. Daniel Ray Pruitt</t>
+  </si>
+  <si>
+    <t>4% per annum</t>
+  </si>
+  <si>
+    <t>11JL00318</t>
+  </si>
+  <si>
+    <t>05/17/2011</t>
+  </si>
+  <si>
+    <t>04/26/2011</t>
+  </si>
+  <si>
+    <t>Moundbuilders Medical Group Inc</t>
+  </si>
+  <si>
+    <t>Voss Harold E</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 10CVF03120, Moundbuilders Medical Group Inc v. Harold Edwin Voss</t>
+  </si>
+  <si>
+    <t>12JL00655</t>
+  </si>
+  <si>
+    <t>09/05/2012</t>
+  </si>
+  <si>
+    <t>08/14/2012</t>
+  </si>
+  <si>
+    <t>Ohio Valley Supply Co</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 12CVF01457, Ohio Valley Supply Co v. Daniel Ray Pruitt</t>
+  </si>
+  <si>
+    <t>3% per annum</t>
+  </si>
+  <si>
+    <t>15JL00932</t>
+  </si>
+  <si>
+    <t>04/22/2015</t>
+  </si>
+  <si>
+    <t>04/02/2015</t>
+  </si>
+  <si>
+    <t>Centerline Credit Corp</t>
+  </si>
+  <si>
+    <t>Kessler Robert L</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 14CVF02871, Centerline Credit Corp v. Robert Lee Kessler</t>
+  </si>
+  <si>
+    <t>16JL00541</t>
+  </si>
+  <si>
+    <t>09/08/2016</t>
+  </si>
+  <si>
+    <t>08/19/2016</t>
+  </si>
+  <si>
+    <t>Newark Orthopaedic Associates Inc</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 16CVF01742, Newark Orthopaedic Associates Inc v. Robert Lee Kessler</t>
+  </si>
+  <si>
+    <t>17JL00288</t>
+  </si>
+  <si>
+    <t>08/14/2017</t>
+  </si>
+  <si>
+    <t>07/21/2017</t>
+  </si>
+  <si>
+    <t>Raccoon Valley Credit Union</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 17CVF00964, Raccoon Valley Credit Union v. Robert Lee Kessler</t>
+  </si>
+  <si>
     <t>20JL00417</t>
   </si>
   <si>
     <t>03/11/2020</t>
   </si>
   <si>
+    <t>02/20/2020</t>
+  </si>
+  <si>
     <t>Heartland Auto Finance Inc</t>
   </si>
   <si>
     <t>Kessler Robert J</t>
   </si>
   <si>
-    <t>Licking Co Municipal 19CVF02288</t>
+    <t>Licking Co Municipal 19CVF02288, Heartland Auto Finance Inc v. Robert John Kessler</t>
   </si>
   <si>
     <t>5% per annum</t>
   </si>
   <si>
-    <t>Active</t>
+    <t>22JL00151</t>
+  </si>
+  <si>
+    <t>02/08/2022</t>
+  </si>
+  <si>
+    <t>01/18/2022</t>
+  </si>
+  <si>
+    <t>Buckeye Lake Marine Sales LLC</t>
+  </si>
+  <si>
+    <t>Licking Co Common Pleas 21CVH00733, Buckeye Lake Marine Sales LLC v. Daniel Robert Pruitt</t>
+  </si>
+  <si>
+    <t>23JL00644</t>
+  </si>
+  <si>
+    <t>05/23/2023</t>
+  </si>
+  <si>
+    <t>05/02/2023</t>
+  </si>
+  <si>
+    <t>Granville Tool &amp; Supply Inc</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 22CVF02209, Granville Tool &amp; Supply Inc v. Daniel Ray Pruitt</t>
+  </si>
+  <si>
+    <t>24JL00902</t>
+  </si>
+  <si>
+    <t>10/03/2024</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>Tri-Valley Equipment Rental Inc</t>
+  </si>
+  <si>
+    <t>Okafor Emeka C</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 24CVF01876, Tri-Valley Equipment Rental Inc v. Emeka Chidi Okafor</t>
+  </si>
+  <si>
+    <t>8% per annum</t>
   </si>
   <si>
     <t>25JL01133</t>
@@ -157,106 +332,154 @@
     <t>07/30/2025</t>
   </si>
   <si>
+    <t>07/09/2025</t>
+  </si>
+  <si>
     <t>Capital Recovery Associates LLC</t>
   </si>
   <si>
-    <t>Okafor Tamsin</t>
-  </si>
-  <si>
-    <t>Licking Co Municipal 25CVF01133</t>
-  </si>
-  <si>
-    <t>8% per annum</t>
-  </si>
-  <si>
-    <t>No judgment liens found against Voss Harold E, Voss Mildred J, Pruitt Daniel R, Pruitt Lorraine K, Kessler Margaret Ann, Kessler Peggy A, Kessler Robert L, or Okafor Emeka.</t>
-  </si>
-  <si>
-    <t>No federal tax liens, state tax liens, or pending suits found against any name searched.</t>
-  </si>
-  <si>
-    <t>Names searched, with the period each name held a record interest in the parcel</t>
+    <t>Bello Tamsin N</t>
+  </si>
+  <si>
+    <t>Licking Co Municipal 25CVF00614, Capital Recovery Associates LLC v. Tamsin Ngozi Bello</t>
+  </si>
+  <si>
+    <t>No certificate was returned under Voss Mildred J, Pruitt Lorraine K, Kessler Margaret Ann, Kessler Peggy A, Okafor Tamsin N, Whitcomb Delaney M, or Whitcomb Sean P.</t>
+  </si>
+  <si>
+    <t>No federal tax lien, state tax lien, or pending foreclosure was returned under any name searched.</t>
+  </si>
+  <si>
+    <t>Licking County Clerk of Courts - entries filed under the certificates on the Judgment Liens tab</t>
+  </si>
+  <si>
+    <t>Every entry docketed after the certificate through 10/02/2026. A certificate with no row here has no later entry.</t>
+  </si>
+  <si>
+    <t>ENTRY DATE</t>
+  </si>
+  <si>
+    <t>ENTRY</t>
+  </si>
+  <si>
+    <t>FILED BY</t>
+  </si>
+  <si>
+    <t>03/05/2015</t>
+  </si>
+  <si>
+    <t>Certificate of judgment refiled</t>
+  </si>
+  <si>
+    <t>06/15/2018</t>
+  </si>
+  <si>
+    <t>Payment credited</t>
+  </si>
+  <si>
+    <t>02/26/2020</t>
+  </si>
+  <si>
+    <t>03/19/2013</t>
+  </si>
+  <si>
+    <t>Satisfaction of judgment filed</t>
+  </si>
+  <si>
+    <t>05/06/2020</t>
+  </si>
+  <si>
+    <t>07/29/2022</t>
+  </si>
+  <si>
+    <t>11/16/2020</t>
+  </si>
+  <si>
+    <t>Order in aid of execution</t>
+  </si>
+  <si>
+    <t>06/27/2022</t>
+  </si>
+  <si>
+    <t>01/22/2025</t>
+  </si>
+  <si>
+    <t>Notice of change of address</t>
+  </si>
+  <si>
+    <t>09/04/2025</t>
+  </si>
+  <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t>08/14/2026</t>
+  </si>
+  <si>
+    <t>08/31/2026</t>
+  </si>
+  <si>
+    <t>Credit of 08/14/2026 vacated; payment returned unpaid</t>
+  </si>
+  <si>
+    <t>Names searched</t>
+  </si>
+  <si>
+    <t>Each name was run as shown and with the given name first.</t>
   </si>
   <si>
     <t>NAME</t>
   </si>
   <si>
-    <t>CAPACITY</t>
-  </si>
-  <si>
-    <t>FROM</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>SOURCE</t>
-  </si>
-  <si>
-    <t>Voss Harold E</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>05/12/1987</t>
-  </si>
-  <si>
-    <t>03/07/2003</t>
-  </si>
-  <si>
-    <t>198705120041 to 200303070115</t>
+    <t>RUN AGAINST</t>
+  </si>
+  <si>
+    <t>SOURCE OF THE NAME</t>
+  </si>
+  <si>
+    <t>Recorder, clerk, probate, domestic relations</t>
+  </si>
+  <si>
+    <t>198705120041</t>
   </si>
   <si>
     <t>Voss Mildred J</t>
   </si>
   <si>
-    <t>Pruitt Daniel R</t>
-  </si>
-  <si>
-    <t>09/19/2014</t>
-  </si>
-  <si>
-    <t>200303070115 to 201409190112</t>
+    <t>200303070115</t>
   </si>
   <si>
     <t>Pruitt Lorraine K</t>
   </si>
   <si>
-    <t>Spouse of owner</t>
-  </si>
-  <si>
-    <t>201103140062 recital</t>
+    <t>200610190027</t>
   </si>
   <si>
     <t>Kessler Margaret Ann</t>
   </si>
   <si>
-    <t>05/04/2018</t>
-  </si>
-  <si>
-    <t>201409190112 to 201805040071</t>
+    <t>201409190112</t>
   </si>
   <si>
     <t>Kessler Peggy A</t>
   </si>
   <si>
-    <t>Owner (name as grantor)</t>
-  </si>
-  <si>
     <t>201805040071</t>
   </si>
   <si>
-    <t>Kessler Robert L</t>
-  </si>
-  <si>
-    <t>current</t>
-  </si>
-  <si>
-    <t>Okafor Emeka</t>
+    <t>Okafor Tamsin N</t>
   </si>
   <si>
     <t>Title order HLT-26-2214</t>
+  </si>
+  <si>
+    <t>Whitcomb Delaney M</t>
+  </si>
+  <si>
+    <t>Clerk</t>
+  </si>
+  <si>
+    <t>Whitcomb Sean P</t>
   </si>
 </sst>
 </file>
@@ -266,7 +489,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,6 +501,11 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -305,7 +533,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -313,25 +541,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,219 +854,271 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="8" width="12" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1712.36</v>
+      </c>
+      <c r="E5" s="5">
+        <v>312.5</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2024.86</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1712.36</v>
+      </c>
+      <c r="E6" s="5">
+        <v>312.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2024.86</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
         <v>2023</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5">
         <v>1741.88</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E7" s="5">
         <v>312.5</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F7" s="5">
         <v>2054.38</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="G7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
         <v>2023</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5">
         <v>1741.88</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E8" s="5">
         <v>312.5</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F8" s="5">
         <v>2054.38</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>2024</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5">
         <v>1768.4</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E9" s="5">
         <v>312.5</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F9" s="5">
         <v>2080.9</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="G9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>2024</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="5">
         <v>1768.4</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E10" s="5">
         <v>312.5</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F10" s="5">
         <v>2080.9</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>2025</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5">
         <v>1796.12</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E11" s="5">
         <v>312.5</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F11" s="5">
         <v>2108.62</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="G11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>2025</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="5">
         <v>1796.12</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E12" s="5">
         <v>312.5</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F12" s="5">
         <v>0</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>25</v>
+      <c r="H12" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -856,124 +1128,388 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>28</v>
+      <c r="A2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>9</v>
+      <c r="D4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="4">
-        <v>4250</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4318.55</v>
+      </c>
+      <c r="H5" s="5">
+        <v>124</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1846.27</v>
+      </c>
+      <c r="H6" s="5">
+        <v>118</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2204.18</v>
+      </c>
+      <c r="H7" s="5">
+        <v>121</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3377.6</v>
+      </c>
+      <c r="H8" s="5">
+        <v>136</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2935.4</v>
+      </c>
+      <c r="H9" s="5">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="5">
+        <v>6118.4</v>
+      </c>
+      <c r="H10" s="5">
+        <v>149</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4251.36</v>
+      </c>
+      <c r="H11" s="5">
         <v>142</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="I11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="F12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="5">
+        <v>14530.75</v>
+      </c>
+      <c r="H12" s="5">
+        <v>212</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="5">
+        <v>3906.2</v>
+      </c>
+      <c r="H13" s="5">
+        <v>131</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="5">
+        <v>5960.12</v>
+      </c>
+      <c r="H14" s="5">
+        <v>164</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="5">
         <v>9412</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H15" s="5">
         <v>187</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>51</v>
+      <c r="I15" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -983,187 +1519,426 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>57</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4" t="s">
         <v>59</v>
       </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2650</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1175</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1175</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>79</v>
+      <c r="B10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/02-title-exam-cedarbrook-lot12/inputs/tax_and_lien_search_hlt262214.xlsx
+++ b/submissions/02-title-exam-cedarbrook-lot12/inputs/tax_and_lien_search_hlt262214.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDD28C1-D24E-1F40-A06E-A12973D11A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A0FE59-D1C1-4346-9486-C5C763C3CF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="161">
   <si>
     <t>Licking County Treasurer - tax duplicate inquiry, parcel 048-112-00.000</t>
   </si>
@@ -38,9 +38,18 @@
     <t>GROSS TAX</t>
   </si>
   <si>
+    <t>ROLLBACK</t>
+  </si>
+  <si>
+    <t>NET TAX</t>
+  </si>
+  <si>
     <t>SPECIAL ASSESSMENT</t>
   </si>
   <si>
+    <t>BILLED</t>
+  </si>
+  <si>
     <t>PAID</t>
   </si>
   <si>
@@ -95,6 +104,9 @@
     <t>07/17/2025</t>
   </si>
   <si>
+    <t>Paid short</t>
+  </si>
+  <si>
     <t>02/18/2026</t>
   </si>
   <si>
@@ -107,6 +119,9 @@
     <t>Unpaid</t>
   </si>
   <si>
+    <t>Rollback is the non-business credit of 10% and the owner-occupancy credit of 2.5% of the gross tax, shown together. The special assessment carries no credit, and the bill is the net tax and the assessment.</t>
+  </si>
+  <si>
     <t>Special assessment: Cedarbrook sanitary sewer improvement, 20 annual installments of 625.00 certified to the duplicate in 2015, collected half with each installment.</t>
   </si>
   <si>
@@ -408,6 +423,12 @@
   </si>
   <si>
     <t>09/04/2025</t>
+  </si>
+  <si>
+    <t>01/15/2026</t>
+  </si>
+  <si>
+    <t>Garnishment credited</t>
   </si>
   <si>
     <t>03/10/2026</t>
@@ -854,28 +875,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -900,225 +922,312 @@
       <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2022</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5">
-        <v>1712.36</v>
+        <v>1712.32</v>
       </c>
       <c r="E5" s="5">
+        <v>214.04</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1498.28</v>
+      </c>
+      <c r="G5" s="5">
         <v>312.5</v>
       </c>
-      <c r="F5" s="5">
-        <v>2024.86</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="5">
+        <v>1810.78</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1810.78</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2022</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5">
-        <v>1712.36</v>
+        <v>1712.32</v>
       </c>
       <c r="E6" s="5">
+        <v>214.04</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1498.28</v>
+      </c>
+      <c r="G6" s="5">
         <v>312.5</v>
       </c>
-      <c r="F6" s="5">
-        <v>2024.86</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="5">
+        <v>1810.78</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1810.78</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2023</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5">
-        <v>1741.88</v>
+        <v>1741.84</v>
       </c>
       <c r="E7" s="5">
+        <v>217.73</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1524.11</v>
+      </c>
+      <c r="G7" s="5">
         <v>312.5</v>
       </c>
-      <c r="F7" s="5">
-        <v>2054.38</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="5">
+        <v>1836.61</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1836.61</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2023</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5">
-        <v>1741.88</v>
+        <v>1741.84</v>
       </c>
       <c r="E8" s="5">
+        <v>217.73</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1524.11</v>
+      </c>
+      <c r="G8" s="5">
         <v>312.5</v>
       </c>
-      <c r="F8" s="5">
-        <v>2054.38</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="5">
+        <v>1836.61</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1836.61</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2024</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5">
-        <v>1768.4</v>
+        <v>1768.48</v>
       </c>
       <c r="E9" s="5">
+        <v>221.06</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1547.42</v>
+      </c>
+      <c r="G9" s="5">
         <v>312.5</v>
       </c>
-      <c r="F9" s="5">
-        <v>2080.9</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="5">
+        <v>1859.92</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1859.92</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2024</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" s="5">
-        <v>1768.4</v>
+        <v>1768.48</v>
       </c>
       <c r="E10" s="5">
+        <v>221.06</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1547.42</v>
+      </c>
+      <c r="G10" s="5">
         <v>312.5</v>
       </c>
-      <c r="F10" s="5">
-        <v>2080.9</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="5">
+        <v>1859.92</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1700</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5">
-        <v>1796.12</v>
+        <v>1796.16</v>
       </c>
       <c r="E11" s="5">
+        <v>224.52</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1571.64</v>
+      </c>
+      <c r="G11" s="5">
         <v>312.5</v>
       </c>
-      <c r="F11" s="5">
-        <v>2108.62</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H11" s="5">
+        <v>1884.14</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1884.14</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5">
-        <v>1796.12</v>
+        <v>1796.16</v>
       </c>
       <c r="E12" s="5">
+        <v>224.52</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1571.64</v>
+      </c>
+      <c r="G12" s="5">
         <v>312.5</v>
       </c>
-      <c r="F12" s="5">
+      <c r="H12" s="5">
+        <v>1884.14</v>
+      </c>
+      <c r="I12" s="5">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1143,61 +1252,61 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G5" s="5">
         <v>4318.55</v>
@@ -1206,27 +1315,27 @@
         <v>124</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G6" s="5">
         <v>1846.27</v>
@@ -1235,27 +1344,27 @@
         <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G7" s="5">
         <v>2204.18</v>
@@ -1264,27 +1373,27 @@
         <v>121</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G8" s="5">
         <v>3377.6</v>
@@ -1293,27 +1402,27 @@
         <v>136</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5">
         <v>2935.4</v>
@@ -1322,27 +1431,27 @@
         <v>133</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G10" s="5">
         <v>6118.4</v>
@@ -1351,27 +1460,27 @@
         <v>149</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G11" s="5">
         <v>4251.36</v>
@@ -1380,27 +1489,27 @@
         <v>142</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G12" s="5">
         <v>14530.75</v>
@@ -1409,27 +1518,27 @@
         <v>212</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G13" s="5">
         <v>3906.2</v>
@@ -1438,27 +1547,27 @@
         <v>131</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G14" s="5">
         <v>5960.12</v>
@@ -1467,27 +1576,27 @@
         <v>164</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G15" s="5">
         <v>9412</v>
@@ -1496,7 +1605,7 @@
         <v>187</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1504,12 +1613,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1519,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -1530,247 +1639,264 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D6" s="5">
         <v>1000</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D16" s="5">
-        <v>2650</v>
+        <v>1500</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D17" s="5">
-        <v>1175</v>
+        <v>2650</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D18" s="5">
         <v>1175</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1175</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1790,155 +1916,155 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
